--- a/results/Int Task Remove ACC -0.7/Rando_3_permute.xlsx
+++ b/results/Int Task Remove ACC -0.7/Rando_3_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7121076597534776</v>
+        <v>0.725143753156801</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6921865745033182</v>
+        <v>0.7227991029409075</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.687823330289673</v>
+        <v>0.7146668669198204</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6767470915222569</v>
+        <v>0.7105496597337806</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6767470915222569</v>
+        <v>0.7031615142515057</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6804249845589343</v>
+        <v>0.6987982700378605</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.68282327401244</v>
+        <v>0.6979256211951315</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6959393866062999</v>
+        <v>0.7003068516124131</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6959393866062999</v>
+        <v>0.6998837171675106</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7015259571702119</v>
+        <v>0.6998837171675106</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7025433440213178</v>
+        <v>0.6995465813691406</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.703100136894369</v>
+        <v>0.6994716623028363</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6996044413992208</v>
+        <v>0.7120156816509489</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7007240066013194</v>
+        <v>0.668178003480747</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.715168261891731</v>
+        <v>0.6690830117323961</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7283116337702792</v>
+        <v>0.6690830117323961</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7312828958012964</v>
+        <v>0.6752179335844235</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7327872565833811</v>
+        <v>0.677016870507494</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7202381371110365</v>
+        <v>0.6760096839048522</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.727070369052024</v>
+        <v>0.6726689266665448</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.733098891760591</v>
+        <v>0.6706614122490211</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7320065858431807</v>
+        <v>0.6717588182906635</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7295495570278305</v>
+        <v>0.6714804218541378</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7366056668359673</v>
+        <v>0.6654842585544911</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7345870728382156</v>
+        <v>0.6634162461115949</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7402086408063402</v>
+        <v>0.6589568030029531</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7335969452717979</v>
+        <v>0.6591602803731743</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7335969452717979</v>
+        <v>0.6724058306027151</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7107378367313057</v>
+        <v>0.6491985066836249</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7012085184033586</v>
+        <v>0.6466018399841298</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7098702880128087</v>
+        <v>0.6366391869628163</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6947994209072734</v>
+        <v>0.6422880142156291</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6719061942943327</v>
+        <v>0.666143229778535</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6692882477661456</v>
+        <v>0.665618796314404</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6668141599145712</v>
+        <v>0.6543280005965386</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6492343834196017</v>
+        <v>0.6713749020424415</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.665048461732185</v>
+        <v>0.656126937519609</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6646100269145866</v>
+        <v>0.6560358387488445</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6123845789126394</v>
+        <v>0.6675642299093796</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6152272826397399</v>
+        <v>0.6538529855775521</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6009967049680134</v>
+        <v>0.6538529855775521</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5892785540127777</v>
+        <v>0.6538529855775521</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.566919081780668</v>
+        <v>0.6476916837726006</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5713308651076935</v>
+        <v>0.6305716219239217</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5718127389144403</v>
+        <v>0.6163836039095794</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5756344906277303</v>
+        <v>0.592588886372046</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5782847965648377</v>
+        <v>0.6037945627751429</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5782635167361456</v>
+        <v>0.6132429825807895</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5782635167361456</v>
+        <v>0.635081362809472</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5426227934048711</v>
+        <v>0.639692402714251</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5051141935402178</v>
+        <v>0.6475990022046606</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5083689521319926</v>
+        <v>0.6405965316341361</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5003865542435144</v>
+        <v>0.6492897813207422</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5023727888323459</v>
+        <v>0.6519196867609216</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.496168048038246</v>
+        <v>0.6260365562835641</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.4998885007323075</v>
+        <v>0.6343552106386481</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5000383388649163</v>
+        <v>0.6244147167777908</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5007398697463444</v>
+        <v>0.6269364644109814</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5055790083107403</v>
+        <v>0.6171116906102844</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.4979933649142405</v>
+        <v>0.6173151679805056</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5022442305284291</v>
+        <v>0.6188084491823622</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.4942405528112588</v>
+        <v>0.6254243655093723</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5007773292794967</v>
+        <v>0.6145090444547932</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.4986514568065203</v>
+        <v>0.596664237366113</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.4990209520138104</v>
+        <v>0.5930552839397439</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.4945129697917883</v>
+        <v>0.5639870379463312</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5002145569504493</v>
+        <v>0.555495506966418</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4997326831437025</v>
+        <v>0.5351171691989076</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5019973141690596</v>
+        <v>0.5296573982753842</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5015205404865448</v>
+        <v>0.52308228294223</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5017989369230704</v>
+        <v>0.5164058685898473</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4993095486988</v>
+        <v>0.5202548795878256</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4991809903948832</v>
+        <v>0.5202548795878256</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4991809903948832</v>
+        <v>0.5036949520729015</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4991809903948832</v>
+        <v>0.5005789520335074</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4989775130246621</v>
+        <v>0.5005789520335074</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4990149725578143</v>
+        <v>0.4909210754016436</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4990149725578143</v>
+        <v>0.4922968778798115</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4998501618673911</v>
+        <v>0.4925003552500327</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4992933689943399</v>
+        <v>0.4935390219298307</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4996092249640177</v>
+        <v>0.4967350411597612</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4996092249640177</v>
+        <v>0.4948662852946183</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4996092249640177</v>
+        <v>0.5029934211914734</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4996092249640177</v>
+        <v>0.4998723210278474</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4999250809336956</v>
+        <v>0.5003380151301341</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5</v>
+        <v>0.5003380151301341</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5</v>
+        <v>0.5013332428207837</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5</v>
+        <v>0.4996092249640177</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5</v>
+        <v>0.4996841440303222</v>
       </c>
     </row>
   </sheetData>
